--- a/results/scraped_Cape_Town_Animal_Welfare.xlsx
+++ b/results/scraped_Cape_Town_Animal_Welfare.xlsx
@@ -49,27 +49,27 @@
     <t>Animal| Definition, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
+    <t>Animals| National Geographic</t>
+  </si>
+  <si>
     <t>AnimalEncyclopedia With Facts, Pictures, Stories, and More!</t>
   </si>
   <si>
-    <t>Animals| National Geographic</t>
+    <t>Animals -NationalGeographic Kids</t>
+  </si>
+  <si>
+    <t>animal|Journal| ScienceDirect.com by Elsevier</t>
+  </si>
+  <si>
+    <t>4K African Wildlife: WildAnimalDiscovery and Beautiful ... - YouTube</t>
   </si>
   <si>
     <t>125 Animals for Kids | Learn WildAnimalNames and Fun Facts |Animal...</t>
   </si>
   <si>
-    <t>Animals -NationalGeographic Kids</t>
-  </si>
-  <si>
-    <t>A-Z Animals - WAF - WorldAnimalFoundation</t>
-  </si>
-  <si>
     <t>Animals: A Complete Guide To TheAnimalKingdom -Active Wild</t>
   </si>
   <si>
-    <t>animal|Journal| ScienceDirect.com by Elsevier</t>
-  </si>
-  <si>
     <t>SPCAof Texas | The leading animal welfare agency in North Texas</t>
   </si>
   <si>
@@ -133,31 +133,31 @@
     <t>Adopt a Dog, Cat, or OtherPetNear You Today | Petfinder</t>
   </si>
   <si>
+    <t>PetSupplies, Accessories, andPetFood -PetStores | PetSmart</t>
+  </si>
+  <si>
+    <t>Pet- Wikipedia</t>
+  </si>
+  <si>
+    <t>Petco:PetSupplies,PetFood, &amp;PetProducts</t>
+  </si>
+  <si>
+    <t>Pet| Definition, Types, History, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>Polyethylene terephthalate- Wikipedia</t>
+  </si>
+  <si>
+    <t>Pet Animals- Types ofPet Animals- A-ZAnimals</t>
+  </si>
+  <si>
+    <t>PetFood, Products and Supplies at Low Prices - Free Shipping</t>
+  </si>
+  <si>
     <t>Adopt aPet: Search Dogs, Cats &amp; Pets for Adoption Near You</t>
   </si>
   <si>
-    <t>SearchPets for AdoptionNear You | Petfinder</t>
-  </si>
-  <si>
-    <t>City ofChicago:: Adopt aPet</t>
-  </si>
-  <si>
-    <t>PetSupplies, Accessories, andPetFood -PetStores | PetSmart</t>
-  </si>
-  <si>
-    <t>Home Page | PAWSChicago</t>
-  </si>
-  <si>
-    <t>Petco:PetSupplies,PetFood, &amp;PetProducts</t>
-  </si>
-  <si>
-    <t>Pet- Wikipedia</t>
-  </si>
-  <si>
-    <t>Animal Care and Control- City ofChicago</t>
-  </si>
-  <si>
-    <t>One Tail at a Time -PetAdoption &amp; Community Building inChicago</t>
+    <t>Home |PetSupplies Plus</t>
   </si>
   <si>
     <t>Dog- Wikipedia</t>
@@ -205,265 +205,265 @@
     <t>Baby Cats - Cute and FunnyCatVideos Compilation #60 | Aww Animals</t>
   </si>
   <si>
-    <t>Cats &amp; Kittens for Adoption in Des Moines, IA | Petfinder</t>
-  </si>
-  <si>
-    <t>Caterpillar Inc. (CAT) Stock Price, News, Quote &amp; History -Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Caterpillar | Caterpillar Inc</t>
-  </si>
-  <si>
     <t>Cat- Simple English Wikipedia, the free encyclopedia</t>
   </si>
   <si>
+    <t>All the Different Types of House Cats, Explained</t>
+  </si>
+  <si>
     <t>Cats Are Just Born to Be Silly FunnyCatVideos 2025</t>
   </si>
   <si>
+    <t>List ofCatBreeds - Types of Cats - Cats.com</t>
+  </si>
+  <si>
+    <t>Products|Cat| Caterpillar</t>
+  </si>
+  <si>
     <t>Bird-Wikipedia</t>
   </si>
   <si>
     <t>Onlinebirdguide,birdID help, life history,birdsounds from Cornell ...</t>
   </si>
   <si>
+    <t>Guide to North American Birds |Audubon</t>
+  </si>
+  <si>
     <t>Bird| Description, Species, Feathers, &amp; Facts | Britannica</t>
   </si>
   <si>
-    <t>Guide to North American Birds |Audubon</t>
-  </si>
-  <si>
     <t>Cornell Lab of Ornithology—Home</t>
   </si>
   <si>
     <t>eBird- Discover a new world of birding...</t>
   </si>
   <si>
-    <t>Bird— Shared Electric Scooters and E-Bikes</t>
-  </si>
-  <si>
-    <t>Magnificent Birds | Stunning Nature | Stress Relief | Relaxing Birds ...</t>
-  </si>
-  <si>
     <t>Birds: Different Types, Definition, Photos, andMore -A-Z Animals</t>
   </si>
   <si>
     <t>Bird- Definition, Types, Characteristics, Habitat, Life span, &amp; Picture</t>
   </si>
   <si>
+    <t>Bird- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Search,All About Birds,Cornell Lab of Ornithology</t>
+  </si>
+  <si>
     <t>Animal Welfare</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d551fc48aeac9251c9217e6b6d7c7aa1345df6dc6b49a9f1e53c70e1d62296bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW5pbWFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fbb717d0868ecac71802db4c7ed656fbdf8b7db2a4395b7ab459b94c793fdee9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20vYW5pbWFscy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60c2170f72724593993cfab5887dd520170e4dd283471327b94eba7ac67269e2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2FuaW1hbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce495afa4c3855008e3eab2c1d63884d448b0663d0a2e781dca48c8c6e790a00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4dc98f8f425d0248795fc4b690122be636bc5c25a1083282c140f0ab2e951134JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9hbmltYWxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c8c51afc04ece328cf50eed10952117bca86c9d48e624a22a7286cc70963352JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1yZWJzR2dZY1pDaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ceb097215a173fa3dad92b861178fa21b2a12f974f69226d50d7f8220fb7630JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly9raWRzLm5hdGlvbmFsZ2VvZ3JhcGhpYy5jb20vYW5pbWFscy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=979e658784fcc1ece18ebcf8ec650ac20c7435591ae17df31adee1a55f4217dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93b3JsZGFuaW1hbGZvdW5kYXRpb24ub3JnL2FuaW1hbHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c111922a9b31bb4d5884e4c673a53307c7644e8de99d889847afe4835de5d8bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93d3cuYWN0aXZld2lsZC5jb20vYW5pbWFscy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef252b917f9d6ebb948d4e414b16384b93ecbf09cd2fa6a9718285928c0b7e01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3997aad7-d483-6463-378a-bd35d5af65a2&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZWRpcmVjdC5jb20vam91cm5hbC9hbmltYWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d96e57b639160faacec1b78d9c7e7834b646b9f3cb628c3dec90a3c90b78188JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9zcGNhLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b70d0d88c96c08c7de9748e318547e3fa83de7f3c84fb729283284c0bc710369JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9zcGNhLm9yZy9yZXNvdXJjZXMvY2xpbmljL2NsaW5pYy1zZXJ2aWNlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3963f67e4420e2c3db55ca79db28c9dfa78af941b07011bcfb97b0e65dc08b57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9ob3VzdG9uc3BjYS5vcmcvYXZhaWxhYmxlLXBldHMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be150db03684064d761017ce35fc4fd27ac224027c48cf5a8b790a13f8e875e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9ob3VzdG9uc3BjYS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2fbb496dfe0f3eb26e8dbcb9681986f18892f43fd0c4c5bb6923a444121fc58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly93d3cuc3BjYWkub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca7a31257de9bbef553c38f7262d3a28802672153cf44f14de71d8252e04cb7dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU29jaWV0eV9mb3JfdGhlX1ByZXZlbnRpb25fb2ZfQ3J1ZWx0eV90b19BbmltYWxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f431f14d40018eb5740d55899f1181d3566bf6e9932b218437aeba89dd098598JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS9tZW1iZXIvdXMvdHgvZGFsbGFzL3NwY2Etb2YtdGV4YXMtZGFsbGFzLXR4MTk4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d2e5b359a3dbe459e28d8145d2953ea06d825a57f9d285871b72d8b92183bd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly9zcGNhZWFzdHR4LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e373c9edfcdd9e50862b9771ce1b9ab629c251f87796b73cf6df5211fba9088aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly93d3cuYXNwY2Eub3JnL2Fkb3B0LXBldC9hZG9wdGFibGUtZG9ncy15b3VyLWxvY2FsLXNoZWx0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2314c1c0f5aab3182d06541c85c6b77cf0c0cc8bbe35827599b7bc382b4c952cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10c717a9-47a9-6356-23eb-004b46af62f6&amp;u=a1aHR0cHM6Ly93d3cubW9iaWxlc3BjYS5vcmcvcGV0cy1hdmFpbGFibGUtZm9yLWFkb3B0aW9uLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=26b0f9f5d105e2d1189dd415a05c70cc9ff31867f254ecc0943d620bd6b776acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2lsZGxpZmU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=beab771433f1ce23f0fcb4364c8014b6d020b1acf679c92d9834b38e94229a0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly90cHdkLnRleGFzLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5065e77518ffc48c16d76ed3bbe844b8c6d96c34a549a65f0ebdd9addc6e589fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ1OTI5NzU0Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=557ea03ab72921267a33148c941796a8303983cf52ad44919dfa81245fe1d58cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cud29ybGR3aWxkbGlmZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acd364ce92a68e0273e99fe8b6d37eaa7f888459bbc7e715d971f5060cc7c657JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9leHBsb3JlL2ZvY3VzL3dpbGRsaWZl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1166c15a0815aacd036271286dd676172fad11375adec889c1f576cbb6a9a8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cubndmLm9yZy9XaWxkbGlmZS5hc3B4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ebeb8a78253987e4aed235a39252c4707f30621cfed0fbee12c0180b34c032cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly90cHdkLnRleGFzLmdvdi9odW50d2lsZC93aWxkLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=828487ca6c8132b40c6683ddbeb99cedc7c919112a4b0b94a9359b4f62794c10JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj01a296dDB1RGE0Yw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f9296b8fcc895566fb64db960dbd5b13b23ed5470c72e91e62f34d984ab78c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1vbzljOUhDLXBtTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6385d1ecf30ac67931520e482595da411ff4af8a00d693713545fdd5465ca25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32e6aa4b-710c-65ad-2332-bda9709f64a2&amp;u=a1aHR0cHM6Ly93aWxkbGlmZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a11df3206880586d19199142fcd20286f2c22be6d04bfc4ddb958d6e52d846f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=04fb1553c97c86d306d99b6e3ac8ddc814f7b0c298f9430de446f993f9e2192aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cuYWRvcHRhcGV0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=488a721d0517fddb8111c3014bc93fcaec50c2c0b80cbe06c11ca28175ef0827JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS9zZWFyY2gvcGV0cy1mb3ItYWRvcHRpb24vdXMvaWwvY2hpY2Fnby8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c223d905d792c4efc572e345da0e618eac6674db382cf2e27ddcbda156781b4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cuY2hpY2Fnby5nb3YvY2l0eS9lbi9kZXB0cy9jYWNjL3Byb3ZkcnMvY2FyZS9zdmNzL2Fkb3B0aW9uLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f63d6b1799bad0b8cf5ef8491bfdbdc18d7616ed5f0afbd91cb42a0321c1ee9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cucGV0c21hcnQuY29tLz9tc29ja2lkPTE1MDhhY2M2MWYwZjZlNTAwYTBhYmIyNDFlMzA2Zjg2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24d6cee7aa74fb8a7861b82156b138d21f4d5a2fcca8ebca9a413285e4b7fd3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cucGF3c2NoaWNhZ28ub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25acf17d850b0053cfb4e8083595829ad84e7fc4c9c4fc2f5db8caace7b23a90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cucGV0Y28uY29tLz9tc29ja2lkPTE1MDhhY2M2MWYwZjZlNTAwYTBhYmIyNDFlMzA2Zjg2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8316150bbbb7cfaa7acf021ee4fc4cda11b02abf8457060c52deb3c0ef02e0cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUGV0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f04be657e1c7c3a57a04a370ced9bf9f832b4e5295ec4cf27072b49ab1f26b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cuY2hpY2Fnby5nb3YvY2l0eS9lbi9kZXB0cy9jYWNjLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66486d6f504b1db1a3802453a646cabbe1839143aeff84464c83d7e0aaea4913JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1508acc6-1f0f-6e50-0a0a-bb241e306f86&amp;u=a1aHR0cHM6Ly93d3cub25ldGFpbC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=581534361d3187e1cb577a67ea9166ac8e7a38a675ae8d5a293bb12204c5fec6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRG9n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d83222b4c9743776621be9be1d32c58b9ded873065b4b6f57d6b09402e916cedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cuYWtjLm9yZy9kb2ctYnJlZWRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aae1a898c6a2f9db737ab1e7db15b2ed791301d4a9c97d480a7de2344fd6fffeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cuZG9nZG9nLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a13491fcfa3b19db6ff1a66ec552b8c1e71cdae68b1db237becd07ba0e0bde7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5oZXBwZXIuY29tL21vc3QtcG9wdWxhci1kb2ctYnJlZWRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=419777560ab9610649872542e7882d77051a507cca9eb52cd2c2dd548299bcb4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2RvZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87ab7a3e24c7a916fdfb42589e04eefbfdd6c24005644dc68e1b0140530e5be1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2RvZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3646a3ec232ce5658846b16e4f781d8c66212a62b4880d6c566c817109b6be58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cuYWtjLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17e0fd5b03eb32cb12e3f933013d57350c383710c6602e20891512a86471cd76JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly93d3cuZG9nYnJlZWRzbGlzdC5pbmZvL2FsbC1kb2ctYnJlZWRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f26f49f2112b7d617b87d042296ca9dc22499985bb5768f98325cf6b8d2d52cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2FuaWRhZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2fc87aa5e2d3a5347eee43976f84c0287d5ec597ca487f076c0a5e06e3ff3e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29ae312a-b114-672e-0708-26c8b0bd662a&amp;u=a1aHR0cHM6Ly9wdXBweWZpbmRlci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da6af7b261dae091a23b6b1347a469e6641fa885308b66033df900be953a0cbfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2F0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2743b8d538ce3a2f3377e292856ffaf50c1c832694a8d200b8731655ce6de5ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cuY2F0LmNvbS9lbl9VUy5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7958259b848b5e099257ae3fed155f59df89a8506d37ce68ee34d188fac43305JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cubmV3d29ybGRlbmN5Y2xvcGVkaWEub3JnL2VudHJ5L0NhdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fb69958c7268eea66633af6fb9983b5c17422c18b8314f0fa6b64e96030adb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2NhdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a5dde2a525ff44d208b9e4ea4329c76a481b450bc4eb4d5f5fdee56ae7d89d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1FOWlQOGpkdFlaMA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54af2afa2f8115244214b5ce4bb5d4e69904c8d9b6dddc9a3ab4048679f6aca9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS9zZWFyY2gvY2F0cy1mb3ItYWRvcHRpb24vdXMvaWEvZGVzbW9pbmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ea1b661f75fa07b7a08bc25662ade2bb58752585c2cc0b4286b13cfde88c468JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly9maW5hbmNlLnlhaG9vLmNvbS9xdW90ZS9DQVQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71ede902e75bde5f13a52e4ca6c13fd6c63b83cfaefcb367057e6f7fdc3088d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cuY2F0ZXJwaWxsYXIuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1ca12ce2929b8896314832fabbca4daad970b683743a97f7b4e73af44a88aa7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0NhdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b799a0ec42d9af538231f33d4b5c1f1eff5369a476950cd9d245d6ad3fd7ac98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d79a087-e31b-655b-07d7-b765e20464c6&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1pSzRXVG5QdXYtdw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c674c4262470369d892a17f032a512b957aace2e1a49c924e661b987782c7d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQmlyZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1abaf716f37d0c01c97c29157eb16b32f7fc1fde1dfadbdb89d582766a120b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly93d3cuYWxsYWJvdXRiaXJkcy5vcmcvbmV3cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5abbe2dbbe4dfbcb84668d2b63de7a60d44a5b51ae9662f1d349cdf35a00373eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2JpcmQtYW5pbWFs&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6309e1ee1733540fb5e859531a6cee8c923f0f08ef8455c364e09376ea66813JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly93d3cuYXVkdWJvbi5vcmcvYmlyZC1ndWlkZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3bcd9f7de3e43b50bef92d777f9828cc0003d57ab7685e98edb6b8c2d0ef677JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly93d3cuYmlyZHMuY29ybmVsbC5lZHUvaG9tZS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=def83c86b8f69089b8accf640bd8632f84a067cdf75a50120941bbd715c2e407JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly9lYmlyZC5vcmcvaG9tZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=994d09f914d9df366a65f91117ab939a9e3532e542f10c8083c0474977b74cb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly9iaXJkLmNvLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d26dffde2271037156b6d4ee82de72ebc8fc4923b6687e9f4c4191d0bc2a7369JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1rc3Bwc294dVhYSQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2777b971ce36cfbf59b0a7910f64b49e01f34ff4af96ab8d0b297ed978b0240dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20vYW5pbWFscy9iaXJkcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d773d56e2033630401052b8df95ccd170dc644bbd706ef20def0958a97e67ef2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=105d230d-e721-6bb7-1725-34efe68a6a5b&amp;u=a1aHR0cHM6Ly9hbmltYWxmYWN0LmNvbS9iaXJkLw&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e81021c25383c882f4cd375c6097ab4c693d8240b1909c2873e82a0ca1ce118aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbmltYWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=abbce76a506822bdcdd6bf692de2f815e2c41ceb4eb252b856ae55be307f101aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20vYW5pbWFscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0906bd5c05c121db4c645de673162665250d5b2c69a96a6fa080f64c45f7b9e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2FuaW1hbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6453e0ac90e5848a789b94bbde2c4d872b23129696436d6ef8d7e1043b5186eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9hbmltYWxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d58ec53b2a2244a9691cf5cd680ee335658ee1f20423c336cf3bc8e0dfcd97fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd821eb89d4b06e5f47e21bf59e3e33de752d6d3ad50cef668fb0b2b923c153aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9raWRzLm5hdGlvbmFsZ2VvZ3JhcGhpYy5jb20vYW5pbWFscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25bdf17aba15f5adf9acfaca2d7b7e75f0223290c92b89e5289b809c94267260JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZWRpcmVjdC5jb20vam91cm5hbC9hbmltYWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d39e9d278dae7f0bda565cd63c49ca5dac87e1cd4fcd676fd6269c9f7cbfebc9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9YkF5dTkzYk5kREk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c5e5e3163e52567a9cd07bdca9fbc05173f35356385cae80ef754bd06e9343aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9cmVic0dnWWNaQ2s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b393c3a039c3395291f3362adcf5182b9d5eb9b72ecb49d5fd6108ce642f784JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ce4e46f-b30f-6c19-0e45-f38db2d46d1a&amp;u=a1aHR0cHM6Ly93d3cuYWN0aXZld2lsZC5jb20vYW5pbWFscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7aafa4f157359c2c6ec01490f2e57a95c8ad85d9a7401128f014a6b2b85ce025JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9zcGNhLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b116feda70480a9324a981323be9197a3684ad73b8a52c2d121b80fa6440a80JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9zcGNhLm9yZy9yZXNvdXJjZXMvY2xpbmljL2NsaW5pYy1zZXJ2aWNlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f4f7961d4353aa503249fda2972bf449d120cdcc1224d37c1c253cbe23457c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9ob3VzdG9uc3BjYS5vcmcvYXZhaWxhYmxlLXBldHMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2119a56ca938db698b84b5d016df2602c8d96e6a88ebef6cb180cb01ab65521dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9ob3VzdG9uc3BjYS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3d3a4ec92301d22006e4d9e85384f23918c99146e0c750931ae0ecc4bec377bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly93d3cuc3BjYWkub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=595fd087d6a243da0ff01388445413cee3606f603cc7c0ee39a97b4e70ce6bdfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU29jaWV0eV9mb3JfdGhlX1ByZXZlbnRpb25fb2ZfQ3J1ZWx0eV90b19BbmltYWxz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c95fc0c41ef3ca9844c6b796dec3bdbc8ff7b390a5ab5f16b6f3340432e3260JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS9tZW1iZXIvdXMvdHgvZGFsbGFzL3NwY2Etb2YtdGV4YXMtZGFsbGFzLXR4MTk4Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9808daf61209e2a0848779e6d89a6483085d91345f7967cfa13babfbe92839b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly9zcGNhZWFzdHR4LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3bb18e16b9b529e59b4ca4409a8c3bc4aaf6e52f03dc657f338f11912878352JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly93d3cuYXNwY2Eub3JnL2Fkb3B0LXBldC9hZG9wdGFibGUtZG9ncy15b3VyLWxvY2FsLXNoZWx0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=543b181775fe3455293503d1115ad67aa3d0a784e5517057177c337b72324a70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e679cb4-8460-6469-3224-8b5685406579&amp;u=a1aHR0cHM6Ly93d3cubW9iaWxlc3BjYS5vcmcvcGV0cy1hdmFpbGFibGUtZm9yLWFkb3B0aW9uLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3077c9ce2fc7e363483e9effda1f74b6903becab597e3213e5d19c39f0e18c3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvV2lsZGxpZmU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=205ba5d1202caea3775ccb8fa702d93c1b3b160a6f7ce6ebcfe9cec9578779c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly90cHdkLnRleGFzLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8531a39032e234d42b07d3625e330f93b73d138c535389b38ae90f7eaed2afcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQ1OTI5NzU0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfa66e7f053996f01e8b47aea1c5236a528f0d38d2a6350dfa4ade2ee62fafd5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cud29ybGR3aWxkbGlmZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28560c3dce762d1adf0284599c3e07be80251ce9c6010a9fcb8eb09bd3e5d4edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9leHBsb3JlL2ZvY3VzL3dpbGRsaWZl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2066117d1937388b5e84c790e50bce28e412e0d2bc91227168eb93f0b480b8c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cubndmLm9yZy9XaWxkbGlmZS5hc3B4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ddbda4bf2a21b22adeca057d6ab20aceed9cb37bffc8b7a11ae184c7c916c0f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly90cHdkLnRleGFzLmdvdi9odW50d2lsZC93aWxkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91af735a2f28481913415b0aa2bd4c4682736364d7194352739e5b90fcaa429dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj01a296dDB1RGE0Yw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c634261b2a1a4116b568732441cf7e32b0a952c2efb833bba713b2e838998042JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1vbzljOUhDLXBtTQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ffb3e5312b50206080cad3ba0760efe6cc6a900c82f20e35633c1f73835b5d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a88436b-ef5f-6e9c-3c83-5489eef86fe7&amp;u=a1aHR0cHM6Ly93aWxkbGlmZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c8b5668ef2a45324ab6f041cc7c75d37cd57ed8baebf50b2761d4851f17bdf0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cucGV0ZmluZGVyLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=19abb74f818d6dd8f94b6a7bfebcedf0f4e0667a851dc49578502ba66eb94bf2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cucGV0c21hcnQuY29tLz9tc29ja2lkPTA0N2E4YjM2NDFkZjYyMTcyOTk1OWNkNDQwYjU2MzRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6fd8216087b4be34b7683bb1696846e843a70bb9d2a88a035b7cde2cc4dd19f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUGV0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05958b9670811b1da0f83276c22ce53bba3365a2c5d053beff2578b431b715a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cucGV0Y28uY29tLz9tc29ja2lkPTA0N2E4YjM2NDFkZjYyMTcyOTk1OWNkNDQwYjU2MzRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=674ccd67098c752856996e66d04169aee847cd7653b2dbe5565b6203e2c6c8b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL3BldA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9bfd33b70b48ac4ecc64b6724a70539d6aca15cad40770cef0dc19af53a0cbd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUG9seWV0aHlsZW5lX3RlcmVwaHRoYWxhdGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f2abfd85e4abf979ce85edbdd357c0c22581a5a9682a3ebea06e4cbfea273a30JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20vcGV0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0047791a7d0f998ad1f181bae490c8ff0b6c4de2cdf227c97015d239129a27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cuY2hld3kuY29tLz9tc29ja2lkPTA0N2E4YjM2NDFkZjYyMTcyOTk1OWNkNDQwYjU2MzRl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3e380b66b104c4bd771e5dfa1cbd5b743e1f2815d70bbb792f3dcfaf1ebaf1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cuYWRvcHRhcGV0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d252ca03405e201dab34d0efd4336f2d859d4b1258a453a2ce113532ec209e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=047a8b36-41df-6217-2995-9cd440b5634e&amp;u=a1aHR0cHM6Ly93d3cucGV0c3VwcGxpZXNwbHVzLmNvbS8_bXNvY2tpZD0wNDdhOGIzNjQxZGY2MjE3Mjk5NTljZDQ0MGI1NjM0ZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d12233319d9b388bfaec1a666354325ca0e479d79a5791af4d23ce8ff89f003bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRG9n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92a65f4fb6b1a4dece25cc40ce5ef4fc9e5af7f7556d4392712715734eb6ab24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cuYWtjLm9yZy9kb2ctYnJlZWRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6272529736a6564464a2777bb923144fe61437fd70bb939354d102abc551fbb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cuZG9nZG9nLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bbb073bd937eb94c2dd40b9ec207c05216b66d15e720623d51cf6f9284338daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly9hcnRpY2xlcy5oZXBwZXIuY29tL21vc3QtcG9wdWxhci1kb2ctYnJlZWRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f139207fd1a544a2c76d2f4088ac917f86b75e903f3660a85745a70d5c049a1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2RvZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10ae28b316955440632833e0690f7783b9bc5baa2884e640278c02f5e77cae42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2RvZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed62d977c490ce469e65cfb0ee6d3aec11c50c92693623939f13377a582347fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cuYWtjLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d25824dc7ccb1a5cb29889548a9beff0cdd85fc9ce66c9c7cd11bd484ffbcee0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly93d3cuZG9nYnJlZWRzbGlzdC5pbmZvL2FsbC1kb2ctYnJlZWRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0d9d30a7be02858580fe85a80475f181d21f75422e54272c44ef57d3b1f6c780JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2FuaWRhZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b1b87628f23f8b29cc15c56481d66d7d8f09a348800265d944dade60e7c93ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10acff11-60c9-6389-1235-e8f361886231&amp;u=a1aHR0cHM6Ly9wdXBweWZpbmRlci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78226e095ea02a7e209b9c9e46e15940329831b9819f42410efcf56af2f547fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2F0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dea25e07c712d358df939bae3ed13d4073c039c41836d1c8ed75c1db5cc9c02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cuY2F0LmNvbS9lbl9VUy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6c159133e455a7375044540a270e092b8275fde8e13565faeac5be751558902JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cubmV3d29ybGRlbmN5Y2xvcGVkaWEub3JnL2VudHJ5L0NhdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a38c1793a67f6a3d970d4e21f2b518337dbe2a391079859bd6b7f36977c0a94JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2NhdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef6a9b905b247f3be4c964326779ce046ba2de873c030137daae53524803b2f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1FOWlQOGpkdFlaMA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2fb72beb341c7d02f31c20a8795de4f181d2329f202f860076e317456f89ee5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0NhdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c4d60a8091c31d7c83126b997d9f7be6f3fada8fd816c6d7d05780f7fc89701JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVHlwZXMtb2YtSG91c2UtQ2F0cw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27d3efe18adbaf17ac908609ca212ab155e87d43ec9de1fd206edbae4dc77479JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1pSzRXVG5QdXYtdw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f30f499906e52968e4b805756fdace905acafcbc6a2575ba2686ec5f2768d408JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly9jYXRzLmNvbS9jYXQtQnJlZWRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f423635617650d14e8bd1223f792b15e796b1a1e70d56038641b92ef458cc951JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4c5d52-2183-6188-2505-4ab02047606d&amp;u=a1aHR0cHM6Ly93d3cuY2F0LmNvbS9lbl9VUy9wcm9kdWN0cy5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=988f96028934601523f8af9e9a4c3a07e612c944d1bf8ad56023bf03dedf1e08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9CaXJk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8054f330b1930e6cd2e89c224ad3fbf2f34130f31f474505561ece6f6a2ae74JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly93d3cuYWxsYWJvdXRiaXJkcy5vcmcvbmV3cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cce12a429acdd10cfd1211918492787a8853fd349258caca345161c30c55b45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly93d3cuYXVkdWJvbi5vcmcvYmlyZC1ndWlkZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=93ae076121c407c15f1ae7b40d75079e31c2535d9a797ec93196c9bcb003bbd1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYW5pbWFsL2JpcmQtYW5pbWFs&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=018a8f9b3e0c62394ce8bf3b481eda72d8bf23f9ab009c3ced5ec79491b45787JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly93d3cuYmlyZHMuY29ybmVsbC5lZHUvaG9tZS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0a541e420f4b1c45c59f9ae28ad1610d54fb61ac4e055b3103a0fe87f521142JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly9lYmlyZC5vcmcvaG9tZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4bec8af8579af5ed5120ec9ff8c3ad67d1b976d86b05a445490f91f90985b09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly9hLXotYW5pbWFscy5jb20vYW5pbWFscy9iaXJkcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=01f2198831a95a2ec52d0835cce211887e8c7552d1412b96a5c1ace49a32880cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly9hbmltYWxmYWN0LmNvbS9iaXJkLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8378360c63dd7d48d1f4ef84bfa1a541416175c6062e21ec85d9b0f5d49972aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvQmlyZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1620d7698a97215be7c146ffa8367f4f13cf7bbc2036f5fd45f99ac6306d5b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0d44c3ef-9b13-692e-18f1-d40d9af868d6&amp;u=a1aHR0cHM6Ly93d3cuYWxsYWJvdXRiaXJkcy5vcmcvZ3VpZGUvc2VhcmNo&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
